--- a/Rapid Cortex Internal Docs/RapidCortex_3Year_Projections_DRAFT.xlsx
+++ b/Rapid Cortex Internal Docs/RapidCortex_3Year_Projections_DRAFT.xlsx
@@ -40,7 +40,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="59">
   <si>
-    <t>Rapid Cortex — 3-Year Projection Model: Assumptions</t>
+    <t>NexCort iQ — 3-Year Projection Model: Assumptions</t>
   </si>
   <si>
     <t>CORE — ACV by plan (real, from internal pricing schedule)</t>
@@ -133,7 +133,7 @@
     <t>General &amp; administrative — fixed $/year</t>
   </si>
   <si>
-    <t>Rapid Cortex — 3-Year Revenue &amp; Cost Projection</t>
+    <t>NexCort iQ — 3-Year Revenue &amp; Cost Projection</t>
   </si>
   <si>
     <t>100% formula-driven from the Assumptions tab. No revenue, customer, or cost figures are hardcoded here — change Assumptions and this entire sheet recalculates.</t>
